--- a/Libraries/Vehicle/Steer/DragLink/sm_car_data_Steer_DragLink.xlsx
+++ b/Libraries/Vehicle/Steer/DragLink/sm_car_data_Steer_DragLink.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28827"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GIT\Others\smiller\ssvt_srcR22a\Libraries\Vehicle\Steer\DragLink\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{85995BAB-6BE6-4CA7-98DF-FC5D8A55A194}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{09FED41A-9561-42E3-92C0-556D0C2FEF10}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="330" yWindow="1020" windowWidth="21600" windowHeight="11235" tabRatio="869" xr2:uid="{3FA59F9D-D9D3-4E28-B3CE-9BFC80E89258}"/>
+    <workbookView xWindow="31110" yWindow="3345" windowWidth="21600" windowHeight="11295" tabRatio="869" xr2:uid="{3FA59F9D-D9D3-4E28-B3CE-9BFC80E89258}"/>
   </bookViews>
   <sheets>
     <sheet name="DragCrossWheelDriven_Landy_f" sheetId="9" r:id="rId1"/>
@@ -896,13 +896,13 @@
         <v>10</v>
       </c>
       <c r="F15" s="15">
-        <v>0.13380000000000003</v>
+        <v>0.14000000000000001</v>
       </c>
       <c r="G15" s="15">
-        <v>-0.375</v>
+        <v>-0.28199999999999997</v>
       </c>
       <c r="H15" s="15">
-        <v>0.45</v>
+        <v>0.47499999999999998</v>
       </c>
       <c r="J15" s="14"/>
     </row>
@@ -931,13 +931,13 @@
         <v>10</v>
       </c>
       <c r="F17" s="15">
-        <v>0.28000000000000003</v>
+        <v>0.32500000000000001</v>
       </c>
       <c r="G17" s="15">
-        <v>-0.375</v>
+        <v>-0.33100000000000002</v>
       </c>
       <c r="H17" s="15">
-        <v>0.45</v>
+        <v>0.41</v>
       </c>
       <c r="J17" s="14"/>
     </row>
@@ -951,13 +951,13 @@
         <v>10</v>
       </c>
       <c r="F18" s="18">
-        <v>0.28000000000000003</v>
+        <v>0.20200000000000001</v>
       </c>
       <c r="G18" s="18">
-        <v>0.61470000000000002</v>
+        <v>0.60399999999999998</v>
       </c>
       <c r="H18" s="18">
-        <v>0.45</v>
+        <v>0.37</v>
       </c>
       <c r="J18" s="19" t="s">
         <v>34</v>
@@ -1070,7 +1070,7 @@
   <sheetPr>
     <tabColor theme="8" tint="-0.249977111117893"/>
   </sheetPr>
-  <dimension ref="A1:O12"/>
+  <dimension ref="A1:S12"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="14.42578125" style="12" customWidth="1"/>
@@ -1082,7 +1082,7 @@
     <col min="11" max="20" width="7.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A1" s="1"/>
       <c r="B1" s="2"/>
       <c r="C1" s="3"/>
@@ -1102,7 +1102,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
         <v>5</v>
       </c>
@@ -1115,7 +1115,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="3" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A3" s="4" t="s">
         <v>7</v>
       </c>
@@ -1127,7 +1127,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="4" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
         <v>8</v>
       </c>
@@ -1141,7 +1141,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
         <v>41</v>
       </c>
@@ -1153,17 +1153,17 @@
         <v>10</v>
       </c>
       <c r="F5" s="15">
-        <v>-0.13</v>
+        <v>-0.14099999999999999</v>
       </c>
       <c r="G5" s="15">
-        <v>-0.375</v>
+        <v>0.13900000000000001</v>
       </c>
       <c r="H5" s="15">
-        <v>0.38</v>
+        <v>0.35399999999999998</v>
       </c>
       <c r="J5" s="14"/>
     </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A6" s="4"/>
       <c r="B6" s="5" t="s">
         <v>10</v>
@@ -1176,7 +1176,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A7" s="4"/>
       <c r="B7" s="5" t="s">
         <v>13</v>
@@ -1191,7 +1191,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A8" s="4"/>
       <c r="B8" s="5" t="s">
         <v>42</v>
@@ -1206,7 +1206,7 @@
         <v>0.2</v>
       </c>
     </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
         <v>24</v>
       </c>
@@ -1218,14 +1218,13 @@
         <v>10</v>
       </c>
       <c r="F9" s="18">
-        <f>2.8-2.9586</f>
-        <v>-0.1586000000000003</v>
+        <v>-0.16600000000000001</v>
       </c>
       <c r="G9" s="18">
-        <v>0.61470000000000002</v>
+        <v>0.61899999999999999</v>
       </c>
       <c r="H9" s="18">
-        <v>0.30499999999999999</v>
+        <v>0.27400000000000002</v>
       </c>
       <c r="J9" s="19" t="s">
         <v>34</v>
@@ -1235,8 +1234,18 @@
       <c r="M9" s="19"/>
       <c r="N9" s="19"/>
       <c r="O9" s="19"/>
-    </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="Q9" s="18">
+        <f>2.8-2.9586</f>
+        <v>-0.1586000000000003</v>
+      </c>
+      <c r="R9" s="18">
+        <v>0.61470000000000002</v>
+      </c>
+      <c r="S9" s="18">
+        <v>0.30499999999999999</v>
+      </c>
+    </row>
+    <row r="10" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A10" s="4"/>
       <c r="B10" s="5" t="s">
         <v>10</v>
@@ -1250,7 +1259,7 @@
       </c>
       <c r="J10" s="14"/>
     </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A11" s="4" t="s">
         <v>29</v>
       </c>
@@ -1276,7 +1285,7 @@
         <v>3.1415700000000002</v>
       </c>
     </row>
-    <row r="12" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A12" s="4"/>
       <c r="B12" s="5" t="s">
         <v>32</v>

--- a/Libraries/Vehicle/Steer/DragLink/sm_car_data_Steer_DragLink.xlsx
+++ b/Libraries/Vehicle/Steer/DragLink/sm_car_data_Steer_DragLink.xlsx
@@ -1,20 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29530"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GIT\Others\smiller\ssvt_srcR22a\Libraries\Vehicle\Steer\DragLink\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\veh-tpl\Libraries\Vehicle\Steer\DragLink\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{09FED41A-9561-42E3-92C0-556D0C2FEF10}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{162A5C59-007E-4534-B718-774811D46AC5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="31110" yWindow="3345" windowWidth="21600" windowHeight="11295" tabRatio="869" xr2:uid="{3FA59F9D-D9D3-4E28-B3CE-9BFC80E89258}"/>
+    <workbookView xWindow="40260" yWindow="0" windowWidth="17445" windowHeight="15585" tabRatio="869" activeTab="2" xr2:uid="{3FA59F9D-D9D3-4E28-B3CE-9BFC80E89258}"/>
   </bookViews>
   <sheets>
-    <sheet name="DragCrossWheelDriven_Landy_f" sheetId="9" r:id="rId1"/>
-    <sheet name="DragCrossActuator_Landy_r" sheetId="10" r:id="rId2"/>
+    <sheet name="CrossWheelDriven_Landy_f" sheetId="9" r:id="rId1"/>
+    <sheet name="CrossActuator_Landy_r" sheetId="10" r:id="rId2"/>
+    <sheet name="CrossActuator_Sedan_HambaLG_r" sheetId="11" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -35,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="92" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="127" uniqueCount="45">
   <si>
     <t>Units</t>
   </si>
@@ -164,14 +165,21 @@
   </si>
   <si>
     <t>xStroke</t>
+  </si>
+  <si>
+    <t>Must be consistent with Left or Right value in Steer</t>
+  </si>
+  <si>
+    <t>DragCrossActuator_Sedan_HambaLG_r</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="1">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="0.000"/>
+    <numFmt numFmtId="165" formatCode="0.0000"/>
   </numFmts>
   <fonts count="3" x14ac:knownFonts="1">
     <font>
@@ -237,7 +245,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -270,13 +278,31 @@
     <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="2" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="164" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="5">
+  <dxfs count="7">
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <fill>
         <patternFill>
@@ -625,7 +651,7 @@
   <sheetPr>
     <tabColor theme="8" tint="-0.249977111117893"/>
   </sheetPr>
-  <dimension ref="A1:T22"/>
+  <dimension ref="A1:T23"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="14.42578125" style="12" customWidth="1"/>
@@ -895,169 +921,185 @@
       <c r="D15" t="s">
         <v>10</v>
       </c>
-      <c r="F15" s="15">
-        <v>0.14000000000000001</v>
-      </c>
-      <c r="G15" s="15">
-        <v>-0.28199999999999997</v>
-      </c>
-      <c r="H15" s="15">
-        <v>0.47499999999999998</v>
+      <c r="F15" s="14">
+        <v>0.14899999999999999</v>
+      </c>
+      <c r="G15" s="14">
+        <v>-0.28299999999999997</v>
+      </c>
+      <c r="H15" s="14">
+        <v>0.55200000000000005</v>
       </c>
       <c r="J15" s="14"/>
     </row>
     <row r="16" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A16" s="4"/>
       <c r="B16" s="5" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="C16" s="5"/>
       <c r="D16" t="s">
-        <v>11</v>
-      </c>
-      <c r="H16">
-        <v>0.05</v>
+        <v>15</v>
+      </c>
+      <c r="F16" s="11"/>
+      <c r="G16" s="11"/>
+      <c r="H16" s="21">
+        <f>7.028*PI()/180</f>
+        <v>0.12266173983016147</v>
       </c>
     </row>
     <row r="17" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A17" s="4" t="s">
-        <v>24</v>
-      </c>
+      <c r="A17" s="4"/>
       <c r="B17" s="5" t="s">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="C17" s="5"/>
       <c r="D17" t="s">
-        <v>10</v>
-      </c>
-      <c r="F17" s="15">
-        <v>0.32500000000000001</v>
-      </c>
-      <c r="G17" s="15">
-        <v>-0.33100000000000002</v>
-      </c>
-      <c r="H17" s="15">
-        <v>0.41</v>
-      </c>
-      <c r="J17" s="14"/>
+        <v>11</v>
+      </c>
+      <c r="H17" s="20">
+        <v>0.05</v>
+      </c>
     </row>
     <row r="18" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A18" s="4"/>
-      <c r="B18" s="19" t="s">
-        <v>26</v>
+      <c r="A18" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="B18" s="5" t="s">
+        <v>25</v>
       </c>
       <c r="C18" s="5"/>
       <c r="D18" t="s">
         <v>10</v>
       </c>
-      <c r="F18" s="18">
-        <v>0.20200000000000001</v>
-      </c>
-      <c r="G18" s="18">
-        <v>0.60399999999999998</v>
-      </c>
-      <c r="H18" s="18">
-        <v>0.37</v>
-      </c>
-      <c r="J18" s="19" t="s">
-        <v>34</v>
-      </c>
-      <c r="K18" s="19"/>
-      <c r="L18" s="19"/>
-      <c r="M18" s="19"/>
-      <c r="N18" s="19"/>
-      <c r="O18" s="19"/>
+      <c r="F18" s="14">
+        <v>0.32100000000000001</v>
+      </c>
+      <c r="G18" s="14">
+        <v>-0.308</v>
+      </c>
+      <c r="H18" s="14">
+        <v>0.45300000000000001</v>
+      </c>
+      <c r="J18" s="14"/>
     </row>
     <row r="19" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A19" s="4"/>
-      <c r="B19" s="5" t="s">
-        <v>10</v>
+      <c r="B19" s="18" t="s">
+        <v>26</v>
       </c>
       <c r="C19" s="5"/>
       <c r="D19" t="s">
+        <v>10</v>
+      </c>
+      <c r="F19" s="19">
+        <v>0.20699999999999999</v>
+      </c>
+      <c r="G19" s="19">
+        <v>0.61</v>
+      </c>
+      <c r="H19" s="19">
+        <v>0.39100000000000001</v>
+      </c>
+      <c r="J19" s="18" t="s">
+        <v>43</v>
+      </c>
+      <c r="K19" s="18"/>
+      <c r="L19" s="18"/>
+      <c r="M19" s="18"/>
+      <c r="N19" s="18"/>
+      <c r="O19" s="18"/>
+    </row>
+    <row r="20" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A20" s="4"/>
+      <c r="B20" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C20" s="5"/>
+      <c r="D20" t="s">
         <v>11</v>
       </c>
-      <c r="H19">
+      <c r="H20">
         <v>0.05</v>
-      </c>
-      <c r="J19" s="14"/>
-    </row>
-    <row r="20" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A20" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="B20" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="C20" s="5"/>
-      <c r="H20" s="15">
-        <v>2</v>
       </c>
       <c r="J20" s="14"/>
     </row>
     <row r="21" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A21" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="B21" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="C21" s="5"/>
+      <c r="H21" s="15">
+        <v>2</v>
+      </c>
+      <c r="J21" s="14"/>
+    </row>
+    <row r="22" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A22" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="B21" s="5" t="s">
+      <c r="B22" s="5" t="s">
         <v>30</v>
-      </c>
-      <c r="C21" s="5"/>
-      <c r="D21" t="s">
-        <v>15</v>
-      </c>
-      <c r="E21" t="s">
-        <v>31</v>
-      </c>
-      <c r="F21" s="11"/>
-      <c r="G21" s="11"/>
-      <c r="H21" s="11">
-        <v>-3.1415700000000002</v>
-      </c>
-      <c r="I21">
-        <v>0</v>
-      </c>
-      <c r="J21">
-        <v>3.1415700000000002</v>
-      </c>
-    </row>
-    <row r="22" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A22" s="4"/>
-      <c r="B22" s="5" t="s">
-        <v>32</v>
       </c>
       <c r="C22" s="5"/>
       <c r="D22" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="E22" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="F22" s="11"/>
       <c r="G22" s="11"/>
       <c r="H22" s="11">
-        <v>0</v>
+        <v>-3.1415700000000002</v>
       </c>
       <c r="I22">
         <v>0</v>
       </c>
       <c r="J22">
+        <v>3.1415700000000002</v>
+      </c>
+    </row>
+    <row r="23" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A23" s="4"/>
+      <c r="B23" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="C23" s="5"/>
+      <c r="D23" t="s">
+        <v>10</v>
+      </c>
+      <c r="E23" t="s">
+        <v>33</v>
+      </c>
+      <c r="F23" s="11"/>
+      <c r="G23" s="11"/>
+      <c r="H23" s="11">
         <v>0</v>
       </c>
+      <c r="I23">
+        <v>0</v>
+      </c>
+      <c r="J23">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="A4:B19 B20">
-    <cfRule type="cellIs" dxfId="4" priority="8" operator="equal">
+  <conditionalFormatting sqref="A4:B20 B21">
+    <cfRule type="cellIs" dxfId="6" priority="8" operator="equal">
       <formula>"class"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A21:B22">
-    <cfRule type="cellIs" dxfId="3" priority="2" operator="equal">
+  <conditionalFormatting sqref="A22:B23">
+    <cfRule type="cellIs" dxfId="5" priority="2" operator="equal">
       <formula>"class"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E5:E22">
-    <cfRule type="cellIs" dxfId="2" priority="1" operator="equal">
+  <conditionalFormatting sqref="E5:E23">
+    <cfRule type="cellIs" dxfId="4" priority="1" operator="equal">
       <formula>"class"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -1152,13 +1194,13 @@
       <c r="D5" t="s">
         <v>10</v>
       </c>
-      <c r="F5" s="15">
+      <c r="F5" s="14">
         <v>-0.14099999999999999</v>
       </c>
-      <c r="G5" s="15">
+      <c r="G5" s="14">
         <v>0.13900000000000001</v>
       </c>
-      <c r="H5" s="15">
+      <c r="H5" s="14">
         <v>0.35399999999999998</v>
       </c>
       <c r="J5" s="14"/>
@@ -1210,40 +1252,285 @@
       <c r="A9" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="B9" s="19" t="s">
+      <c r="B9" s="18" t="s">
         <v>26</v>
       </c>
       <c r="C9" s="5"/>
       <c r="D9" t="s">
         <v>10</v>
       </c>
-      <c r="F9" s="18">
-        <v>-0.16600000000000001</v>
-      </c>
-      <c r="G9" s="18">
-        <v>0.61899999999999999</v>
-      </c>
-      <c r="H9" s="18">
-        <v>0.27400000000000002</v>
-      </c>
-      <c r="J9" s="19" t="s">
+      <c r="F9" s="19">
+        <v>-0.126</v>
+      </c>
+      <c r="G9" s="19">
+        <v>0.61299999999999999</v>
+      </c>
+      <c r="H9" s="19">
+        <v>0.26500000000000001</v>
+      </c>
+      <c r="J9" s="18" t="s">
         <v>34</v>
       </c>
-      <c r="K9" s="19"/>
-      <c r="L9" s="19"/>
-      <c r="M9" s="19"/>
-      <c r="N9" s="19"/>
-      <c r="O9" s="19"/>
-      <c r="Q9" s="18">
-        <f>2.8-2.9586</f>
-        <v>-0.1586000000000003</v>
-      </c>
-      <c r="R9" s="18">
-        <v>0.61470000000000002</v>
-      </c>
-      <c r="S9" s="18">
-        <v>0.30499999999999999</v>
-      </c>
+      <c r="K9" s="18"/>
+      <c r="L9" s="18"/>
+      <c r="M9" s="18"/>
+      <c r="N9" s="18"/>
+      <c r="O9" s="18"/>
+      <c r="Q9" s="15"/>
+      <c r="R9" s="15"/>
+      <c r="S9" s="15"/>
+    </row>
+    <row r="10" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A10" s="4"/>
+      <c r="B10" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C10" s="5"/>
+      <c r="D10" t="s">
+        <v>11</v>
+      </c>
+      <c r="H10">
+        <v>0.05</v>
+      </c>
+      <c r="J10" s="14"/>
+    </row>
+    <row r="11" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A11" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="B11" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="C11" s="5"/>
+      <c r="D11" t="s">
+        <v>15</v>
+      </c>
+      <c r="E11" t="s">
+        <v>40</v>
+      </c>
+      <c r="F11" s="11"/>
+      <c r="G11" s="11"/>
+      <c r="H11" s="11">
+        <v>-3.1415700000000002</v>
+      </c>
+      <c r="I11">
+        <v>0</v>
+      </c>
+      <c r="J11">
+        <v>3.1415700000000002</v>
+      </c>
+    </row>
+    <row r="12" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A12" s="4"/>
+      <c r="B12" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="C12" s="5"/>
+      <c r="D12" t="s">
+        <v>10</v>
+      </c>
+      <c r="E12" t="s">
+        <v>40</v>
+      </c>
+      <c r="F12" s="11"/>
+      <c r="G12" s="11"/>
+      <c r="H12" s="11">
+        <v>0</v>
+      </c>
+      <c r="I12">
+        <v>0</v>
+      </c>
+      <c r="J12">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <conditionalFormatting sqref="A4:B12">
+    <cfRule type="cellIs" dxfId="3" priority="2" operator="equal">
+      <formula>"class"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E5:E12">
+    <cfRule type="cellIs" dxfId="2" priority="1" operator="equal">
+      <formula>"class"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F63655A8-9F5E-41AA-BC8E-0B64CE68E0E3}">
+  <sheetPr>
+    <tabColor theme="8" tint="-0.249977111117893"/>
+  </sheetPr>
+  <dimension ref="A1:S12"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="14.42578125" style="12" customWidth="1"/>
+    <col min="2" max="2" width="12.7109375" customWidth="1"/>
+    <col min="3" max="5" width="11.140625" customWidth="1"/>
+    <col min="6" max="8" width="10" customWidth="1"/>
+    <col min="9" max="9" width="7.28515625" customWidth="1"/>
+    <col min="10" max="10" width="8.42578125" customWidth="1"/>
+    <col min="11" max="20" width="7.28515625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A1" s="1"/>
+      <c r="B1" s="2"/>
+      <c r="C1" s="3"/>
+      <c r="D1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="H1" s="2" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A2" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="B2" s="5"/>
+      <c r="C2" s="5"/>
+      <c r="E2" s="6"/>
+      <c r="F2" s="6"/>
+      <c r="G2" s="6"/>
+      <c r="H2" s="7" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A3" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="B3" s="5"/>
+      <c r="C3" s="5"/>
+      <c r="F3" s="6"/>
+      <c r="G3" s="6"/>
+      <c r="H3" s="7" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A4" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="B4" s="8"/>
+      <c r="C4" s="8"/>
+      <c r="D4" s="8"/>
+      <c r="E4" s="8"/>
+      <c r="F4" s="9"/>
+      <c r="G4" s="9"/>
+      <c r="H4" s="10" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A5" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="B5" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C5" s="5"/>
+      <c r="D5" t="s">
+        <v>10</v>
+      </c>
+      <c r="F5" s="14">
+        <v>-0.14099999999999999</v>
+      </c>
+      <c r="G5" s="14">
+        <v>0.13900000000000001</v>
+      </c>
+      <c r="H5" s="14">
+        <v>0.35399999999999998</v>
+      </c>
+      <c r="J5" s="14"/>
+    </row>
+    <row r="6" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A6" s="4"/>
+      <c r="B6" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C6" s="5"/>
+      <c r="D6" t="s">
+        <v>11</v>
+      </c>
+      <c r="H6">
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="7" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A7" s="4"/>
+      <c r="B7" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C7" s="5"/>
+      <c r="D7" t="s">
+        <v>14</v>
+      </c>
+      <c r="F7" s="11"/>
+      <c r="G7" s="11"/>
+      <c r="H7" s="11">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="8" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A8" s="4"/>
+      <c r="B8" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="C8" s="5"/>
+      <c r="D8" t="s">
+        <v>10</v>
+      </c>
+      <c r="F8" s="11"/>
+      <c r="G8" s="11"/>
+      <c r="H8" s="11">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="9" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A9" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="B9" s="18" t="s">
+        <v>26</v>
+      </c>
+      <c r="C9" s="5"/>
+      <c r="D9" t="s">
+        <v>10</v>
+      </c>
+      <c r="F9" s="19">
+        <v>-0.126</v>
+      </c>
+      <c r="G9" s="19">
+        <v>0.61299999999999999</v>
+      </c>
+      <c r="H9" s="19">
+        <v>0.26500000000000001</v>
+      </c>
+      <c r="J9" s="18" t="s">
+        <v>34</v>
+      </c>
+      <c r="K9" s="18"/>
+      <c r="L9" s="18"/>
+      <c r="M9" s="18"/>
+      <c r="N9" s="18"/>
+      <c r="O9" s="18"/>
+      <c r="Q9" s="15"/>
+      <c r="R9" s="15"/>
+      <c r="S9" s="15"/>
     </row>
     <row r="10" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A10" s="4"/>
